--- a/backend/radionet_irrigation_system.xlsx
+++ b/backend/radionet_irrigation_system.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
